--- a/app/templates/report/nra.xlsx
+++ b/app/templates/report/nra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\oimbra\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B91D0C-4329-4F2F-986F-CEE476800F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E8B91E-FC08-4D58-A6A8-0FC883881301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recursos" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recursos!$A$2:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reservas!$A$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reservas!$A$2:$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Recursos</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>Marketplace</t>
   </si>
 </sst>
 </file>
@@ -624,16 +627,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="24.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="24.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="61.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="24.88671875" style="1"/>
+    <col min="1" max="1" width="21.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="61.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="24.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -641,7 +644,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" s="5" customFormat="1" ht="25.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="5" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -655,7 +658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="9"/>
       <c r="C3" s="3"/>
@@ -675,20 +678,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="24.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="24.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="57.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.6640625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="24.88671875" style="1"/>
+    <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="57.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.7109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="24.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -699,8 +703,9 @@
       <c r="F1" s="12"/>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
+      <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="25.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -725,8 +730,11 @@
       <c r="H2" s="11" t="s">
         <v>7</v>
       </c>
+      <c r="I2" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -739,11 +747,12 @@
       <c r="H3" s="16" t="s">
         <v>10</v>
       </c>
+      <c r="I3" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A2:I2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="D3:D99999">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(A3&lt;&gt;"",LEN(D3)&lt;&gt;53)</formula>
     </cfRule>
   </conditionalFormatting>
